--- a/02_TRAVAIL/Lot1_Hostaway/MASTER_CTRL_HA_Anomalies.xlsx
+++ b/02_TRAVAIL/Lot1_Hostaway/MASTER_CTRL_HA_Anomalies.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,10 +466,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>56388919</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -479,7 +481,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Listing 515523 dans API Hostaway absent de REF_Logements</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -489,22 +491,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:25:32+00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>c80f75e2c2ced949</t>
+          <t>35b6409bd8dac984</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60559486</v>
+        <v>62163639</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,7 +516,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>listingMapId 556954 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -524,18 +526,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:00+00:00</t>
+          <t>2026-08-17T05:25:33+00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>e7905ded3cc345af</t>
+          <t>a2e76d281b8f48e7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60457618</v>
+        <v>53642724</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -559,18 +561,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:04+00:00</t>
+          <t>2026-08-17T05:25:46+00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9a22be546b868196</t>
+          <t>b897388b0fc70e12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60375992</v>
+        <v>57476381</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -594,18 +596,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:05+00:00</t>
+          <t>2026-08-17T05:25:46+00:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>f7a61a92484830f9</t>
+          <t>b2227bff4207fb4f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53642724</v>
+        <v>59855296</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -629,18 +631,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:05+00:00</t>
+          <t>2026-08-17T05:25:51+00:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>b897388b0fc70e12</t>
+          <t>30c3fc316dd71f87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57476381</v>
+        <v>55624233</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -664,18 +666,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:05+00:00</t>
+          <t>2026-08-17T05:26:02+00:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>b2227bff4207fb4f</t>
+          <t>f1f0ed9ffb8acb16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>59855296</v>
+        <v>57780060</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -699,22 +701,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:19+00:00</t>
+          <t>2026-08-17T05:26:12+00:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30c3fc316dd71f87</t>
+          <t>7f00f74b6ccd7d59</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58933140</v>
+        <v>53642723</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -724,7 +726,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -734,22 +736,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4faa0afb698ce591</t>
+          <t>5db0c8c0d73594c3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>58765312</v>
+        <v>53642721</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -759,7 +761,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -769,22 +771,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>44394137836938f1</t>
+          <t>04d3b82e8dfed93a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>58607186</v>
+        <v>53642719</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -794,7 +796,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -804,22 +806,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2e21a8143d7edd48</t>
+          <t>6305bfbfee01e5c8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>58607180</v>
+        <v>53642717</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -829,7 +831,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -839,22 +841,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>a8b82879770ec804</t>
+          <t>97a792f13f3d4161</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>58607170</v>
+        <v>53642716</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -864,7 +866,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -874,22 +876,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ffc168e9bc4a5570</t>
+          <t>d355c09efe23bb0c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>58607164</v>
+        <v>53642715</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -899,7 +901,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -909,22 +911,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10e0d618ad3c4b4a</t>
+          <t>bebc1835093e7b2e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>58607160</v>
+        <v>53642714</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -934,7 +936,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -944,22 +946,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>02a4783687a129f1</t>
+          <t>64065de7e4a0bb89</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>58607154</v>
+        <v>53642713</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -969,7 +971,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -979,22 +981,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9bddb3b84c702e58</t>
+          <t>0d62385c48bf192f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>58607149</v>
+        <v>53642712</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1014,22 +1016,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8dcd17b4f4c85681</t>
+          <t>8ad5ad1ced79520e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>58607145</v>
+        <v>53642711</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1039,7 +1041,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1049,22 +1051,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>233304f61704c892</t>
+          <t>b18108f5bd5a3b56</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>58607138</v>
+        <v>53642710</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1074,7 +1076,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1084,22 +1086,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>b107e43a75299747</t>
+          <t>7fbdf874f2ba46c7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>58607127</v>
+        <v>53642709</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1109,7 +1111,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1119,22 +1121,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>b3a46187c9af79ce</t>
+          <t>7337335d823e9648</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>58607119</v>
+        <v>53642708</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1144,7 +1146,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1154,22 +1156,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0cf9246c8ab05c30</t>
+          <t>7a071bc6fb71d425</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>58607115</v>
+        <v>53642706</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1179,7 +1181,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1189,22 +1191,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7c4807d83f737bac</t>
+          <t>a2e76874f8d9cf97</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>58607112</v>
+        <v>53642705</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1214,7 +1216,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1224,22 +1226,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>88e739d99967279b</t>
+          <t>66ad98e02366208a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>58607111</v>
+        <v>53642704</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1249,7 +1251,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1259,22 +1261,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>e45ec71d5624a2ec</t>
+          <t>d560176cf578f66f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>58607108</v>
+        <v>53642703</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1284,7 +1286,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1294,22 +1296,22 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>881afc7568e4214c</t>
+          <t>0841ebef24ae92cc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>58607104</v>
+        <v>53642701</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1319,7 +1321,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1329,22 +1331,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9ffa18e123daa01b</t>
+          <t>d781a8a5355a2f4d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>58607096</v>
+        <v>53642700</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1354,7 +1356,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1364,22 +1366,22 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2dfab9dd3a303160</t>
+          <t>01d9c142633225ac</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>58606195</v>
+        <v>53642699</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1389,7 +1391,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1399,22 +1401,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>833a686f40d4bf05</t>
+          <t>e7bae1aefbce6c76</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>58606185</v>
+        <v>53642698</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LISTING_ORPHELIN_A_CONTROLER</t>
+          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1424,7 +1426,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>listingMapId 515523 absent de REF_Logements — Lot 2 requis</t>
+          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1434,18 +1436,18 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>bb8a437d2c62e830</t>
+          <t>3ae5c1dbc4e26d40</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>55624233</v>
+        <v>53642697</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1469,18 +1471,18 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:38+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>f1f0ed9ffb8acb16</t>
+          <t>7f5721336ba0ebdb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>57780060</v>
+        <v>53642696</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1504,18 +1506,18 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:57+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7f00f74b6ccd7d59</t>
+          <t>f23984f6149f0a1b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>56388919</v>
+        <v>53642695</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1539,850 +1541,10 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:18+00:00</t>
+          <t>2026-08-17T05:26:40+00:00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
-        <is>
-          <t>35b6409bd8dac984</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>53642723</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>5db0c8c0d73594c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>53642721</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>04d3b82e8dfed93a</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>53642719</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6305bfbfee01e5c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>53642717</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>97a792f13f3d4161</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>53642716</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>d355c09efe23bb0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>53642715</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>bebc1835093e7b2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>53642714</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>64065de7e4a0bb89</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>53642713</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0d62385c48bf192f</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>53642712</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>8ad5ad1ced79520e</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>53642711</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>b18108f5bd5a3b56</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>53642710</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>7fbdf874f2ba46c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>53642709</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>7337335d823e9648</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>53642708</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>7a071bc6fb71d425</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>53642706</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>a2e76874f8d9cf97</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>53642705</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>66ad98e02366208a</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>53642704</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>d560176cf578f66f</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>53642703</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>0841ebef24ae92cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>53642701</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>d781a8a5355a2f4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>53642700</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>01d9c142633225ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>53642699</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>e7bae1aefbce6c76</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>53642698</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>3ae5c1dbc4e26d40</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53642697</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>7f5721336ba0ebdb</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>53642696</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>f23984f6149f0a1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>53642695</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>VRBO_MONTANT_NON_RENSEIGNE</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>VRBO paymentStatus=Unknown — saisie manuelle requise au Lot 4</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:37+00:00</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>a63e93469e8d9f96</t>
         </is>
